--- a/tools/importer/reports/import-brand-page.report.xlsx
+++ b/tools/importer/reports/import-brand-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,22 +37,43 @@
     <t>url</t>
   </si>
   <si>
+    <t>ru/monitor-buying-guide.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product"]</t>
+  </si>
+  <si>
+    <t>ru/monitor-buying-guide</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>monitor-buying-guide</t>
+  </si>
+  <si>
+    <t>2026-03-24T12:27:37.854Z</t>
+  </si>
+  <si>
+    <t>Руководство для мониторов LG | LG Россия Business</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ru/monitor-buying-guide</t>
+  </si>
+  <si>
     <t>ae/better-life/index.report.json</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>["hero-campaign","columns-storytell","carousel-upcycle","columns-feature","cards-product","cards-benefit","cards-story"]</t>
   </si>
   <si>
     <t>ae/better-life/index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>brand-page</t>
   </si>
   <si>
-    <t>2026-03-19T18:46:52.411Z</t>
+    <t>2026-05-26T11:24:04.643Z</t>
   </si>
   <si>
     <t>Better life for all | LG UAE</t>
@@ -489,13 +510,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -604,6 +623,32 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
